--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -2047,38 +2047,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128757614</v>
+        <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>100779</v>
+        <v>91678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>653517</v>
+        <v>653501</v>
       </c>
       <c r="R14" t="n">
-        <v>6674785</v>
+        <v>6674769</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2121,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,37 +2157,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128757594</v>
+        <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>91678</v>
+        <v>100779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>653501</v>
+        <v>653517</v>
       </c>
       <c r="R15" t="n">
-        <v>6674769</v>
+        <v>6674785</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128757576</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>128757567</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128757574</v>
       </c>
       <c r="B6" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128757580</v>
       </c>
       <c r="B10" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128757577</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91679</v>
+        <v>91706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91018</v>
+        <v>91023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91706</v>
+        <v>91711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91711</v>
+        <v>91716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128757576</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>128757567</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128757574</v>
       </c>
       <c r="B6" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128757580</v>
       </c>
       <c r="B10" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128757577</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91716</v>
+        <v>91720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128757576</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>128757567</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128757574</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128757580</v>
       </c>
       <c r="B10" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128757577</v>
       </c>
       <c r="B13" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91720</v>
+        <v>91725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91044</v>
+        <v>91047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91047</v>
+        <v>91050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128757576</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>128757567</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128757574</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128757580</v>
       </c>
       <c r="B10" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91050</v>
+        <v>91054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128757577</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757604</v>
       </c>
       <c r="B2" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128757576</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>128757567</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128757574</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128757616</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128757580</v>
       </c>
       <c r="B10" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>128757615</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>128757585</v>
       </c>
       <c r="B12" t="n">
-        <v>91054</v>
+        <v>91063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128757577</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>128757594</v>
       </c>
       <c r="B14" t="n">
-        <v>91745</v>
+        <v>91754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128757614</v>
       </c>
       <c r="B15" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128757600</v>
       </c>
       <c r="B16" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128757617</v>
       </c>
       <c r="B17" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>128757619</v>
       </c>
       <c r="B18" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128757618</v>
       </c>
       <c r="B19" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>93216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>93216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>92871</v>
+        <v>93216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40406-2025 artfynd.xlsx
+++ b/artfynd/A 40406-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128757610</v>
       </c>
       <c r="B3" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128757608</v>
       </c>
       <c r="B8" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128757612</v>
       </c>
       <c r="B9" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
